--- a/specs/Test Scripts.xlsx
+++ b/specs/Test Scripts.xlsx
@@ -8,12 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Justin Ryan Uy\Documents\Code\CCPROG3-MCO\specs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0ACA6E17-4E97-4398-B4DE-D43E0BAC9CE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE6F2CFC-46A3-4042-A83D-C4D564AE7089}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C6577B9E-10DE-44C3-9E79-3F56380D2A0E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="4" xr2:uid="{C6577B9E-10DE-44C3-9E79-3F56380D2A0E}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Coffee" sheetId="1" r:id="rId1"/>
+    <sheet name="CustomSpecialCoffee" sheetId="2" r:id="rId2"/>
+    <sheet name="SpecialCoffee" sheetId="3" r:id="rId3"/>
+    <sheet name="CoffeeTruck" sheetId="4" r:id="rId4"/>
+    <sheet name="SpecialCoffeeTruck" sheetId="9" r:id="rId5"/>
+    <sheet name="StorageBin" sheetId="6" r:id="rId6"/>
+    <sheet name="Money" sheetId="7" r:id="rId7"/>
+    <sheet name="User" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,15 +42,197 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="57">
+  <si>
+    <t>Class: Coffee</t>
+  </si>
+  <si>
+    <t>Method</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>Test Description</t>
+  </si>
+  <si>
+    <t>Sample Input Data</t>
+  </si>
+  <si>
+    <t>Expected Output</t>
+  </si>
+  <si>
+    <t>Actual Output</t>
+  </si>
+  <si>
+    <t>P/F</t>
+  </si>
+  <si>
+    <t>Class: CustomSpecialCoffee</t>
+  </si>
+  <si>
+    <t>Class: SpecialCoffee</t>
+  </si>
+  <si>
+    <t>Class: CoffeeTruck</t>
+  </si>
+  <si>
+    <t>Class: SpecialCoffeeTruck</t>
+  </si>
+  <si>
+    <t>Class: StorageBin</t>
+  </si>
+  <si>
+    <t>Class: Money</t>
+  </si>
+  <si>
+    <t>Class: User</t>
+  </si>
+  <si>
+    <t>Positive</t>
+  </si>
+  <si>
+    <t>Zero</t>
+  </si>
+  <si>
+    <t>Negative</t>
+  </si>
+  <si>
+    <t>IllegalArgumentException</t>
+  </si>
+  <si>
+    <t>P</t>
+  </si>
+  <si>
+    <t>addCoffeeTruck</t>
+  </si>
+  <si>
+    <t>new Money</t>
+  </si>
+  <si>
+    <t>setCoffeeTruckLocation</t>
+  </si>
+  <si>
+    <t>Different locations</t>
+  </si>
+  <si>
+    <t>Same locations</t>
+  </si>
+  <si>
+    <t>Same instance</t>
+  </si>
+  <si>
+    <t>Invalid index</t>
+  </si>
+  <si>
+    <t>"h", 100</t>
+  </si>
+  <si>
+    <t>Valid</t>
+  </si>
+  <si>
+    <t>IndexOutOfBoundsException</t>
+  </si>
+  <si>
+    <t>addQuantity</t>
+  </si>
+  <si>
+    <t>Valid addition</t>
+  </si>
+  <si>
+    <t>Results in zero</t>
+  </si>
+  <si>
+    <t>Above the max capacity</t>
+  </si>
+  <si>
+    <t>Results in negative</t>
+  </si>
+  <si>
+    <t>(Given "a") "b"</t>
+  </si>
+  <si>
+    <t>(Given "c") "c"</t>
+  </si>
+  <si>
+    <t>(Given "d") "d"</t>
+  </si>
+  <si>
+    <t>(Given "e") "f", 0</t>
+  </si>
+  <si>
+    <t>(Given "g") "g", 0</t>
+  </si>
+  <si>
+    <t>(Max 40, Quantity 10), 10</t>
+  </si>
+  <si>
+    <t>(Max 40, Quantity 10), -Quantity</t>
+  </si>
+  <si>
+    <t>(Max 40, Quantity 10), 50</t>
+  </si>
+  <si>
+    <t>(Max 40, Quantity 10), -50</t>
+  </si>
+  <si>
+    <t>ArithmeticException</t>
+  </si>
+  <si>
+    <t>makeCoffee</t>
+  </si>
+  <si>
+    <t>Enough stock</t>
+  </si>
+  <si>
+    <t>Not enough stock</t>
+  </si>
+  <si>
+    <t>No stock</t>
+  </si>
+  <si>
+    <t>(Coffee Medium Latte) Storage Bins generated with stock</t>
+  </si>
+  <si>
+    <t>(Coffee Medium Latte) Storage Bins generated with stock; storageBin[0] emptied</t>
+  </si>
+  <si>
+    <t>Coffee Medium Latte $24.00</t>
+  </si>
+  <si>
+    <t>(Coffee Medium Latte) Storage Bins all empty</t>
+  </si>
+  <si>
+    <t>Coffee Medium Latte $35.00</t>
+  </si>
+  <si>
+    <t>(Coffee Medium Light Latte Hazelnut Strong shot) Storage Bins generated with stock</t>
+  </si>
+  <si>
+    <t>(Coffee Medium Light Latte Hazelnut Strong shot) Storage Bins generated with stock; specialStorageBin[0] emptied</t>
+  </si>
+  <si>
+    <t>(Coffee Medium Light Latte Hazelnut Strong shot) Storage Bins all empty</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -66,8 +255,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -402,9 +595,850 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{579E42B4-E94A-4DA1-ADB9-2487D7DC023C}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="2.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="4.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.88671875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39CB71C0-1681-4B84-A71B-C47ACB3549A0}">
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="2.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="4.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.88671875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB0778A0-C181-4631-8BE8-5CFF4397817F}">
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="2.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="4.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.88671875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7265631-D0E9-43F6-9D74-E04CF7144234}">
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="2.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="73.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="26.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="4.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.88671875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" s="1">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B4" s="1">
+        <v>2</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B5" s="1">
+        <v>3</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD3805E4-160E-476E-9697-FE1D52B4BE96}">
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="2.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="105" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="26.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="4.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.88671875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" s="1">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B4" s="1">
+        <v>2</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B5" s="1">
+        <v>3</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5895779E-E5BD-4669-A5AD-A8FC1B7A0266}">
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="2.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="4.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.88671875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" s="1">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E3" s="1">
+        <v>20</v>
+      </c>
+      <c r="F3" s="1">
+        <v>20</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B4" s="1">
+        <v>2</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E4" s="1">
+        <v>0</v>
+      </c>
+      <c r="F4" s="1">
+        <v>0</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B5" s="1">
+        <v>3</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B6" s="1">
+        <v>4</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA5E8967-A69E-49A7-9D1C-3F1367528989}">
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="2.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="24.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="4.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.88671875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="1">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="1">
+        <v>1</v>
+      </c>
+      <c r="E3" s="1">
+        <v>1</v>
+      </c>
+      <c r="F3" s="1">
+        <v>1</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B4" s="1">
+        <v>2</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="1">
+        <v>0</v>
+      </c>
+      <c r="E4" s="1">
+        <v>0</v>
+      </c>
+      <c r="F4" s="1">
+        <v>0</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B5" s="1">
+        <v>3</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="1">
+        <v>-1</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0F4294E-6683-4271-9172-D4CBFEDF5C7F}">
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="22.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="2.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="26.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="4.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.88671875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="1">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B4" s="1">
+        <v>2</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B5" s="1">
+        <v>3</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="1">
+        <v>1</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B7" s="1">
+        <v>2</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B8" s="1">
+        <v>3</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/specs/Test Scripts.xlsx
+++ b/specs/Test Scripts.xlsx
@@ -8,19 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Justin Ryan Uy\Documents\Code\CCPROG3-MCO\specs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE6F2CFC-46A3-4042-A83D-C4D564AE7089}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A6F83FC-33D8-4989-98EB-BB267D1096BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="4" xr2:uid="{C6577B9E-10DE-44C3-9E79-3F56380D2A0E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C6577B9E-10DE-44C3-9E79-3F56380D2A0E}"/>
   </bookViews>
   <sheets>
-    <sheet name="Coffee" sheetId="1" r:id="rId1"/>
-    <sheet name="CustomSpecialCoffee" sheetId="2" r:id="rId2"/>
-    <sheet name="SpecialCoffee" sheetId="3" r:id="rId3"/>
-    <sheet name="CoffeeTruck" sheetId="4" r:id="rId4"/>
-    <sheet name="SpecialCoffeeTruck" sheetId="9" r:id="rId5"/>
-    <sheet name="StorageBin" sheetId="6" r:id="rId6"/>
-    <sheet name="Money" sheetId="7" r:id="rId7"/>
-    <sheet name="User" sheetId="8" r:id="rId8"/>
+    <sheet name="CoffeeTruck" sheetId="4" r:id="rId1"/>
+    <sheet name="SpecialCoffeeTruck" sheetId="9" r:id="rId2"/>
+    <sheet name="StorageBin" sheetId="6" r:id="rId3"/>
+    <sheet name="Money" sheetId="7" r:id="rId4"/>
+    <sheet name="User" sheetId="8" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,10 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="57">
-  <si>
-    <t>Class: Coffee</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="54">
   <si>
     <t>Method</t>
   </si>
@@ -67,12 +61,6 @@
   </si>
   <si>
     <t>P/F</t>
-  </si>
-  <si>
-    <t>Class: CustomSpecialCoffee</t>
-  </si>
-  <si>
-    <t>Class: SpecialCoffee</t>
   </si>
   <si>
     <t>Class: CoffeeTruck</t>
@@ -594,178 +582,10 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{579E42B4-E94A-4DA1-ADB9-2487D7DC023C}">
-  <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="13.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="2.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="4.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.88671875" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39CB71C0-1681-4B84-A71B-C47ACB3549A0}">
-  <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="13.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="2.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="4.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.88671875" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB0778A0-C181-4631-8BE8-5CFF4397817F}">
-  <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="13.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="2.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="4.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.88671875" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7265631-D0E9-43F6-9D74-E04CF7144234}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
@@ -780,7 +600,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -791,48 +611,48 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B3" s="1">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>49</v>
-      </c>
       <c r="E3" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -840,19 +660,19 @@
         <v>2</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="E4" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -860,19 +680,19 @@
         <v>3</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -880,11 +700,15 @@
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup scale="76" fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD3805E4-160E-476E-9697-FE1D52B4BE96}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
@@ -899,7 +723,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -910,48 +734,48 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B3" s="1">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -959,19 +783,19 @@
         <v>2</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -979,19 +803,19 @@
         <v>3</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -999,11 +823,15 @@
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup scale="63" fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5895779E-E5BD-4669-A5AD-A8FC1B7A0266}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1019,7 +847,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1030,39 +858,39 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B3" s="1">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E3" s="1">
         <v>20</v>
@@ -1071,7 +899,7 @@
         <v>20</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -1079,10 +907,10 @@
         <v>2</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E4" s="1">
         <v>0</v>
@@ -1091,7 +919,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -1099,19 +927,19 @@
         <v>3</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -1119,19 +947,19 @@
         <v>4</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -1139,11 +967,15 @@
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA5E8967-A69E-49A7-9D1C-3F1367528989}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1158,7 +990,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1169,36 +1001,36 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B3" s="1">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -1210,7 +1042,7 @@
         <v>1</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -1218,7 +1050,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D4" s="1">
         <v>0</v>
@@ -1230,7 +1062,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -1238,19 +1070,19 @@
         <v>3</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D5" s="1">
         <v>-1</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -1258,11 +1090,15 @@
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0F4294E-6683-4271-9172-D4CBFEDF5C7F}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1277,7 +1113,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1288,48 +1124,48 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="1">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="1">
-        <v>1</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>23</v>
-      </c>
       <c r="D3" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -1337,19 +1173,19 @@
         <v>2</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -1357,42 +1193,42 @@
         <v>3</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B6" s="1">
         <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -1400,19 +1236,19 @@
         <v>2</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -1420,19 +1256,19 @@
         <v>3</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F8" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -1440,5 +1276,6 @@
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>